--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:54</t>
+          <t>2026-09-14 12:51:18</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:55</t>
+          <t>2026-09-14 12:51:19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:55</t>
+          <t>2026-09-14 12:51:19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:56</t>
+          <t>2026-09-14 12:51:20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:56</t>
+          <t>2026-09-14 12:51:20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:57</t>
+          <t>2026-09-14 12:51:21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ7" t="b">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:58</t>
+          <t>2026-09-14 12:51:22</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:58</t>
+          <t>2026-09-14 12:51:22</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:58</t>
+          <t>2026-09-14 12:51:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:58</t>
+          <t>2026-09-14 12:51:22</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:58</t>
+          <t>2026-09-14 12:51:23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:59</t>
+          <t>2026-09-14 12:51:24</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-07 12:24:59</t>
+          <t>2026-09-14 12:51:24</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:00</t>
+          <t>2026-09-14 12:51:25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:01</t>
+          <t>2026-09-14 12:51:26</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:01</t>
+          <t>2026-09-14 12:51:26</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -3121,26 +3121,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>끝장</t>
+          <t>표절의혹</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>844588</t>
+          <t>846106</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:01</t>
+          <t>2026-09-14 12:51:27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3164,214 +3164,52 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>떨어지면 끝장</t>
+          <t>표절의혹</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>떨어지면 끝장 (총 70화/완결)</t>
+          <t>표절의혹 (총 29화/미완결)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>총 70화/완결</t>
+          <t>총 29화/미완결</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>완결</t>
+          <t>미완결</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
+          <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
+          <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>6039213</t>
+          <t>13575121</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
-        <is>
-          <t>떨어지면 끝장 (총 70화/완결)
-평점
-9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료
-“떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
-        </is>
-      </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>3.9만</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>39000</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>32</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>표절의혹</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>846106</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:02</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>표절의혹</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>표절의혹 (총 29화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>총 29화/미완결</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>29</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>13575121</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3379,155 +3217,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C19" t="n">
         <v>40</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단말인가</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853619&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>853619</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:02</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:28</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R19" t="n">
         <v>6</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14563924</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>14563924</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)
 평점
@@ -3535,155 +3373,155 @@
 타인의 시선속에서만 살아왔던 정숙녀(23세, 공시생)는 지쳤다. 좋아하는 것도 없고 해야 될 일들만 가득한 인생... 더는 이렇게 살기 싫어!! 기분전환이라도 할까 들어간 미용실에서. 어랏? 뿅! 대머리가 되어버렸다. 오늘부터 대머..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C20" t="n">
         <v>88</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>850210</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:03</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:29</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R20" t="n">
         <v>14</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3691,6 +3529,162 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>나의 경험</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>853278</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:30</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>나의 경험</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>나의 경험 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>14532341</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>나의 경험 (총 6화/미완결)
+평점
+7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료
+살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
+        </is>
+      </c>
       <c r="Y21" t="b">
         <v>0</v>
       </c>
@@ -3735,7 +3729,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3745,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3770,7 +3764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:04</t>
+          <t>2026-09-14 12:51:30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3891,7 +3885,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3901,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3926,7 +3920,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:04</t>
+          <t>2026-09-14 12:51:30</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -4047,7 +4041,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -4063,26 +4057,26 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>나의 경험</t>
+          <t>당신에게 얽힌 채</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>853278</t>
+          <t>849879</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:04</t>
+          <t>2026-09-14 12:51:32</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -4110,21 +4104,21 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>나의 경험</t>
+          <t>당신에게 얽힌 채</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>나의 경험 (총 6화/미완결)</t>
+          <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>총 6화/미완결</t>
+          <t>총 10화/미완결</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4133,181 +4127,25 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
+          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
+          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>14532341</t>
+          <t>14041685</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
-        <is>
-          <t>나의 경험 (총 6화/미완결)
-평점
-7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료
-살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
-        </is>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>66</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>849879</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:06</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채 (총 10화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>총 10화/미완결</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>10</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>14041685</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4315,155 +4153,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:08</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:34</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R25" t="n">
         <v>94</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4471,155 +4309,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C26" t="n">
         <v>9</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:08</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:34</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R26" t="n">
         <v>126</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4627,161 +4465,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG27" t="n">
+      <c r="AG26" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C27" t="n">
         <v>10</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:08</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:34</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R27" t="n">
         <v>47</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4789,155 +4627,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C28" t="n">
         <v>12</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:08</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:34</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R28" t="n">
         <v>31</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4945,155 +4783,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>39</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C29" t="n">
+        <v>37</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:09</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:35</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R29" t="n">
         <v>219</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -5101,161 +4939,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE29" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG29" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>59</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C30" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:09</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:35</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5263,6 +5101,168 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>7.2만</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>66</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>843866</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:36</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>총 42화/미완결</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>42</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>13253015</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
+평점
+9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료
+영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
+        </is>
+      </c>
       <c r="Y31" t="b">
         <v>0</v>
       </c>
@@ -5270,37 +5270,31 @@
         <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>matched</t>
+          <t>review_needed</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>first_non_compilation_numeric_download</t>
+          <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>7.2만</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>72000</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>not_found</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -5313,7 +5307,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5323,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5348,7 +5342,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:09</t>
+          <t>2026-09-14 12:51:36</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5469,42 +5463,42 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>죽여주는 캐스팅</t>
+          <t>만취남녀</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>843866</t>
+          <t>846883</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:09</t>
+          <t>2026-09-14 12:51:37</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -5519,12 +5513,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5532,21 +5526,21 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>죽여주는 캐스팅 [독점]</t>
+          <t>19금 만취남녀</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
+          <t>19금 만취남녀 (총 26화/미완결)</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>총 42화/미완결</t>
+          <t>총 26화/미완결</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -5555,30 +5549,29 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>13253015</t>
+          <t>13646371</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
+          <t>19금 만취남녀 (총 26화/미완결)
 평점
-9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료
-영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
+9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
       <c r="Y33" t="b">
@@ -5625,7 +5618,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -5641,26 +5634,26 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>846883</t>
+          <t>827190</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:11</t>
+          <t>2026-09-14 12:51:37</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5688,21 +5681,21 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>19금 만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>19금 만취남녀 (총 26화/미완결)</t>
+          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>총 26화/미완결</t>
+          <t>총 106화/미완결</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5711,180 +5704,25 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>13646371</t>
+          <t>11253061</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)
-평점
-9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>827190</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:11</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>총 106화/미완결</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>106</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>11253061</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -5892,155 +5730,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
         <v>105</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE35" t="n">
+      <c r="AE34" t="n">
         <v>4</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>9</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:11</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:37</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R35" t="n">
         <v>32</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -6048,6 +5886,161 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>36</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>초임계지옥</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>854340</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:38</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>총 4화/미완결</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>4</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>14649867</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)
+평점
+10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
       <c r="Y36" t="b">
         <v>0</v>
       </c>
@@ -6092,7 +6085,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6120,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:12</t>
+          <t>2026-09-14 12:51:38</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6248,7 +6241,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -6264,26 +6257,26 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>초임계지옥</t>
+          <t>데스루프</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>854340</t>
+          <t>852086</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:12</t>
+          <t>2026-09-14 12:51:39</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6311,21 +6304,21 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>19금 초임계지옥</t>
+          <t>데스루프</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>19금 초임계지옥 (총 4화/미완결)</t>
+          <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>총 4화/미완결</t>
+          <t>총 6화/미완결</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6334,180 +6327,25 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>14649867</t>
+          <t>14366954</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥 (총 4화/미완결)
-평점
-10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>53</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>데스루프</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>852086</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:12</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>데스루프</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>데스루프 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>6</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>14366954</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6515,155 +6353,155 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>105</v>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
+      <c r="AI38" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C39" t="n">
         <v>3</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:14</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:41</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R39" t="n">
         <v>8</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -6671,155 +6509,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA40" t="n">
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
         <v>105</v>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr">
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C40" t="n">
         <v>6</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=832566&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>832566</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:15</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:41</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>총 93화/미완결</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R40" t="n">
         <v>93</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11636787</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>11636787</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)
 평점
@@ -6827,155 +6665,155 @@
 제국의 국정을 마음대로 주무르는 비선실세 환관, 이철수.절대 권력에 돈 많고, 무공까지 강하지만.. 그게 무슨 의미가 있지? '그걸' 못하는데!!환생대법을 통해, 고자가 되기 전으로 회귀한 철수의 목표는 하나다.알파메일이 되..</t>
         </is>
       </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="Y40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
         <v>105</v>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr">
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AI40" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>10</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C41" t="n">
+        <v>11</v>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>851385</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:15</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:41</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="R41" t="n">
         <v>8</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14245757</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>14245757</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)
 평점
@@ -6983,6 +6821,161 @@
 절망의 끝에서 나를 구원해준 남자, 범도건.작고 지켜야할 애기님이라며 내 고백을 짓밞았던 그때와는 다르게...이 남자, 남편 역할을 해도 너무 잘한다.낮에는 세상 든든한 보호자이던 그가 밤만 되면 맹수처럼 집착하며 나를 ..</t>
         </is>
       </c>
+      <c r="Y41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>시루/24/1km</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>850068</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:41</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km (총 12화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>총 12화/미완결</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>12</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>14081030</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km (총 12화/미완결)
+평점
+10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
       <c r="Y42" t="b">
         <v>0</v>
       </c>
@@ -7027,7 +7020,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -7043,26 +7036,26 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>시루/24/1km</t>
+          <t>지옥심판</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>850068</t>
+          <t>854096</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:15</t>
+          <t>2026-09-14 12:51:42</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7090,21 +7083,21 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>19금 시루/24/1km</t>
+          <t>지옥심판</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>19금 시루/24/1km (총 12화/미완결)</t>
+          <t>지옥심판 (총 7화/미완결)</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>총 12화/미완결</t>
+          <t>총 7화/미완결</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -7113,180 +7106,25 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>14081030</t>
+          <t>14622042</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
-        <is>
-          <t>19금 시루/24/1km (총 12화/미완결)
-평점
-10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
-        </is>
-      </c>
-      <c r="Y43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>40</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>854096</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:16</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>총 7화/미완결</t>
-        </is>
-      </c>
-      <c r="R44" t="n">
-        <v>7</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>14622042</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
         <is>
           <t>지옥심판 (총 7화/미완결)
 평점
@@ -7294,155 +7132,155 @@
 죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="Y43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
         <v>105</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE44" t="n">
+      <c r="AE43" t="n">
         <v>2</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr">
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AI43" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>43</v>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C44" t="n">
+        <v>42</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>서바이브</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>838594</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:16</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:42</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N45" t="n">
+      <c r="N44" t="n">
         <v>2</v>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R44" t="n">
         <v>42</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7450,6 +7288,168 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>5.6천</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>5600</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>인터뷰</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>854396</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:42</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재]</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>총 53화/완결</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>53</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=3181357</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>3181357</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)
+평점
+9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료
+특종보다는 흥미를 느끼는 취재거리만 찾는 도윤에게 구 남친이 연락해 귀가 솔깃한 제안을 한다.바로 자신의 심리치료 환자인 연쇄 살인범과의 인터뷰를 진행하는 것.자신의 은밀한 사생활(?!)을 유지하고 싶었던 도윤은 이 ..</t>
+        </is>
+      </c>
       <c r="Y45" t="b">
         <v>0</v>
       </c>
@@ -7457,11 +7457,11 @@
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7475,15 +7475,15 @@
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>5.6천</t>
+          <t>30.1만</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>5600</v>
+        <v>301000</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -7516,26 +7516,26 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>화스트 페이스</t>
+          <t>꿈에서 본 그놈이 대단해!</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>847905</t>
+          <t>854132</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:16</t>
+          <t>2026-09-14 12:51:43</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -7563,48 +7563,204 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>꿈에서 본 그놈이 대단해! [독점]</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>6</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>14626941</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
+평점
+8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
+MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
+        </is>
+      </c>
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>52</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>847905</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:43</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>화스트 페이스</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>24</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7612,162 +7768,6 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>52</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해!</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>854132</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:16</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점]</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
-        <v>6</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>14626941</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
-평점
-8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
-MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
-        </is>
-      </c>
       <c r="Y47" t="b">
         <v>0</v>
       </c>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-09-07 13:14:01</t>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
@@ -7828,26 +7828,26 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>인터뷰</t>
+          <t>나의 비발디</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>854396</t>
+          <t>854344</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25:16</t>
+          <t>2026-09-14 12:51:43</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -7875,210 +7875,48 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>살인자와의 인터뷰 [개정판][컬러연재]</t>
+          <t>나의 비발디</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)</t>
+          <t>나의 비발디 (총 6화/미완결)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>총 53화/완결</t>
+          <t>총 6화/미완결</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>완결</t>
+          <t>미완결</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=3181357</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>3181357</t>
+          <t>14580181</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
-        <is>
-          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)
-평점
-9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료
-특종보다는 흥미를 느끼는 취재거리만 찾는 도윤에게 구 남친이 연락해 귀가 솔깃한 제안을 한다.바로 자신의 심리치료 환자인 연쇄 살인범과의 인터뷰를 진행하는 것.자신의 은밀한 사생활(?!)을 유지하고 싶었던 도윤은 이 ..</t>
-        </is>
-      </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>30.1만</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>301000</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>77</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>나의 비발디</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>854344</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:16</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>나의 비발디</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>나의 비발디 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R49" t="n">
-        <v>6</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>14580181</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
         <is>
           <t>나의 비발디 (총 6화/미완결)
 평점
@@ -8086,155 +7924,155 @@
 "갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
         <v>105</v>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr">
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>84</v>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C49" t="n">
+        <v>85</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>823476</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:17</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:44</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="inlineStr">
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="R49" t="n">
         <v>115</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -8242,155 +8080,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
         <v>105</v>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr">
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>91</v>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C50" t="n">
+        <v>90</v>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:25:17</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:51:44</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="inlineStr">
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="R50" t="n">
         <v>128</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -8398,51 +8236,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA51" t="n">
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
         <v>105</v>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE51" t="n">
+      <c r="AE50" t="n">
         <v>2</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr">
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI51" t="inlineStr">
+      <c r="AI50" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:14:01</t>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:34:14</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:18</t>
+          <t>2026-09-21 12:50:02</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:19</t>
+          <t>2026-09-21 12:50:02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:19</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:20</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:20</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:21</t>
+          <t>2026-09-21 12:50:04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:22</t>
+          <t>2026-09-21 12:50:05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:22</t>
+          <t>2026-09-21 12:50:05</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:22</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:22</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:23</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
+          <t>2026-09-21 12:50:07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
+          <t>2026-09-21 12:50:07</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:25</t>
+          <t>2026-09-21 12:50:08</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:26</t>
+          <t>2026-09-21 12:50:09</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:26</t>
+          <t>2026-09-21 12:50:09</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:27</t>
+          <t>2026-09-21 12:50:10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:28</t>
+          <t>2026-09-21 12:50:10</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:29</t>
+          <t>2026-09-21 12:50:12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:30</t>
+          <t>2026-09-21 12:50:13</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3749,22 +3749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>소꿉친구 컴플렉스</t>
+          <t>럭키비치</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>822640</t>
+          <t>852498</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:30</t>
+          <t>2026-09-21 12:50:13</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3779,61 +3779,217 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>럭키비치 (총 8화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>총 8화/미완결</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>14424733</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>럭키비치 (총 8화/미완결)
+평점
+10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료
+“그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
+        </is>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>소꿉친구 컴플렉스</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>822640</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:13</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>80</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3841,155 +3997,2511 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE23" t="n">
         <v>3</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C24" t="n">
+        <v>69</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>당신에게 얽힌 채</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>849879</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:15</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>당신에게 얽힌 채</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>당신에게 얽힌 채 (총 10화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>총 10화/미완결</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>14041685</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>당신에게 얽힌 채 (총 10화/미완결)
+평점
+10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료
+상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
+        </is>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>841624</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:16</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님 (총 94화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>총 94화/미완결</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>94</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>12998643</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님 (총 94화/미완결)
+평점
+9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료
+사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
+        </is>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>7</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>네가 사는 그 집</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>842465</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:16</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>네가 사는 그 집</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>네가 사는 그 집 (총 47화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>총 47화/미완결</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>47</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>13090391</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>네가 사는 그 집 (총 47화/미완결)
+평점
+9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료
+찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
+        </is>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>두 얼굴</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>845646</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:16</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>두 얼굴의 대표님</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>두 얼굴의 대표님 (총 126화/완결)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>총 126화/완결</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>126</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>6489984</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>두 얼굴의 대표님 (총 126화/완결)
+평점
+6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료
+재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
+        </is>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>157.5만</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>11</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>그리디</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>845919</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:16</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>그리디</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>그리디 (총 31화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>총 31화/미완결</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>31</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>13530624</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>그리디 (총 31화/미완결)
+평점
+9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료
+파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
+        </is>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>37</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>사자의 서</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>823737</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:17</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>사자의서 [도시정벌 레거시]</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>총 219화/완결</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>219</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2737090</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>사자의서 [도시정벌 레거시] (총 219화/완결)
+평점
+9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료
+죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
+        </is>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>121.3만</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1213000</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>박제</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>846363</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:18</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>박제하는 시간</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>박제하는 시간 (총 28화/완결)</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>총 28화/완결</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>28</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>10632769</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>박제하는 시간 (총 28화/완결)
+평점
+10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료
+박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
+        </is>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>7.2만</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>68</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>843866</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:18</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>총 42화/미완결</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>42</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>13253015</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
+평점
+9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료
+영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
+        </is>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>69</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>사탄의 순애</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>845378</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:18</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>사탄의 순애 [독점]</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>사탄의 순애 [독점] (총 35화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>총 35화/미완결</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>35</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>13451638</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>사탄의 순애 [독점] (총 35화/미완결)
+평점
+9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료
+초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
+        </is>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>시든 꽃에 눈물을</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>827190</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:19</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>시든 꽃에 눈물을</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>총 106화/미완결</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>106</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>11253061</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>시든 꽃에 눈물을 (총 106화/미완결)
+평점
+9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료
+남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
+        </is>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>만취남녀</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>846883</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:19</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>19금 만취남녀</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>총 26화/미완결</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>26</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>13646371</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)
+평점
+9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>둘째에게</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>845711</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:19</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>둘째에게</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>둘째에게 (총 32화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>총 32화/미완결</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>32</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>13512084</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>둘째에게 (총 32화/미완결)
+평점
+10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료
+슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
+        </is>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>29</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>초임계지옥</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>854340</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:20</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>총 4화/미완결</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>4</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>14649867</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)
+평점
+10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>37</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>연애 못하면 죽음!</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846662&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>846662</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:20</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>연애 못하면 죽음!</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>연애 못하면 죽음! (총 31화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>총 31화/미완결</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>31</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13633976</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>13633976</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>연애 못하면 죽음! (총 31화/미완결)
+평점
+9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료
+똥차들과의 망한 연애로 인해사랑, 연애에 부정적인 30대가 된 워커홀릭 문주경은어느날 우연히 '금방 사랑에 빠지는' 저주에 걸리게 된다.마음에 드는 상대에게 다짜고짜 고백부터 하게 되는 끔찍한 저주.사랑에 빠지기를 거..</t>
+        </is>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>56</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>데스루프</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>852086</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:21</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>데스루프</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>데스루프 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>6</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>14366954</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>데스루프 (총 6화/미완결)
+평점
+8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료
+정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
+        </is>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:30</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:23</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R39" t="n">
         <v>8</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3997,2518 +6509,6 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>68</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>849879</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:32</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채 (총 10화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>총 10화/미완결</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>10</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>14041685</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채 (총 10화/미완결)
-평점
-10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료
-상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
-        </is>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>841624</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:34</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님 (총 94화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>총 94화/미완결</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>94</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>12998643</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님 (총 94화/미완결)
-평점
-9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료
-사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
-        </is>
-      </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>9</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>두 얼굴</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>845646</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:34</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>두 얼굴의 대표님</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>두 얼굴의 대표님 (총 126화/완결)</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>총 126화/완결</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>126</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>6489984</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>두 얼굴의 대표님 (총 126화/완결)
-평점
-6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료
-재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
-        </is>
-      </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>157.5만</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>10</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>네가 사는 그 집</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>842465</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:34</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>네가 사는 그 집</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>네가 사는 그 집 (총 47화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>총 47화/미완결</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>47</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>13090391</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>네가 사는 그 집 (총 47화/미완결)
-평점
-9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료
-찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
-        </is>
-      </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>12</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>그리디</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>845919</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:34</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>그리디</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>그리디 (총 31화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>총 31화/미완결</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>31</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>13530624</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>그리디 (총 31화/미완결)
-평점
-9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료
-파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
-        </is>
-      </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>37</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>사자의 서</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>823737</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:35</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>사자의서 [도시정벌 레거시]</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>총 219화/완결</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>219</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>2737090</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>사자의서 [도시정벌 레거시] (총 219화/완결)
-평점
-9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료
-죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
-        </is>
-      </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>121.3만</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1213000</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>60</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>박제</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>846363</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:35</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>2</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>박제하는 시간</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>박제하는 시간 (총 28화/완결)</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>총 28화/완결</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
-        <v>28</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>10632769</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>박제하는 시간 (총 28화/완결)
-평점
-10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료
-박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
-        </is>
-      </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>7.2만</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>72000</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>66</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>843866</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:36</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅 [독점]</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>총 42화/미완결</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
-        <v>42</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>13253015</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
-평점
-9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료
-영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
-        </is>
-      </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>67</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>사탄의 순애</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>845378</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:36</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>사탄의 순애 [독점]</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>사탄의 순애 [독점] (총 35화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>총 35화/미완결</t>
-        </is>
-      </c>
-      <c r="R32" t="n">
-        <v>35</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>13451638</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>사탄의 순애 [독점] (총 35화/미완결)
-평점
-9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료
-초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
-        </is>
-      </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>만취남녀</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>846883</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:37</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>19금 만취남녀</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>총 26화/미완결</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>26</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>13646371</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)
-평점
-9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>827190</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:37</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>총 106화/미완결</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>106</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>11253061</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을 (총 106화/미완결)
-평점
-9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료
-남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
-        </is>
-      </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>둘째에게</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>845711</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:37</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>둘째에게</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>둘째에게 (총 32화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>총 32화/미완결</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>32</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>13512084</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>둘째에게 (총 32화/미완결)
-평점
-10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료
-슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
-        </is>
-      </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>36</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>초임계지옥</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>854340</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:38</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥 (총 4화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>총 4화/미완결</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>4</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>14649867</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥 (총 4화/미완결)
-평점
-10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>37</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>연애 못하면 죽음!</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846662&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>846662</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:38</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>연애 못하면 죽음!</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>연애 못하면 죽음! (총 31화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>총 31화/미완결</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
-        <v>31</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13633976</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>13633976</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>연애 못하면 죽음! (총 31화/미완결)
-평점
-9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료
-똥차들과의 망한 연애로 인해사랑, 연애에 부정적인 30대가 된 워커홀릭 문주경은어느날 우연히 '금방 사랑에 빠지는' 저주에 걸리게 된다.마음에 드는 상대에게 다짜고짜 고백부터 하게 되는 끔찍한 저주.사랑에 빠지기를 거..</t>
-        </is>
-      </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>53</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>데스루프</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>852086</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:39</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>데스루프</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>데스루프 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>6</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>14366954</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>데스루프 (총 6화/미완결)
-평점
-8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료
-정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
-        </is>
-      </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>럭키비치</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>852498</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:41</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>thu,sun</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>thu,sun</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>럭키비치</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>럭키비치 (총 8화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>총 8화/미완결</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>14424733</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>럭키비치 (총 8화/미완결)
-평점
-10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료
-“그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
-        </is>
-      </c>
       <c r="Y39" t="b">
         <v>0</v>
       </c>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:41</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:41</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:41</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:42</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7192,26 +7192,26 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>서바이브</t>
+          <t>인터뷰</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>838594</t>
+          <t>854396</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:42</t>
+          <t>2026-09-21 12:50:24</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7235,52 +7235,370 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재]</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>총 53화/완결</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>53</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=3181357</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3181357</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)
+평점
+9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료
+특종보다는 흥미를 느끼는 취재거리만 찾는 도윤에게 구 남친이 연락해 귀가 솔깃한 제안을 한다.바로 자신의 심리치료 환자인 연쇄 살인범과의 인터뷰를 진행하는 것.자신의 은밀한 사생활(?!)을 유지하고 싶었던 도윤은 이 ..</t>
+        </is>
+      </c>
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>30.1만</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>301000</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해!</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>854132</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:24</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점]</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>6</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>14626941</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
+평점
+8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
+MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
+        </is>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>47</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>서바이브</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>838594</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:24</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
         <v>2</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R46" t="n">
         <v>42</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7288,375 +7606,57 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>100</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE44" t="n">
+      <c r="AE46" t="n">
         <v>2</v>
       </c>
-      <c r="AF44" t="inlineStr">
+      <c r="AF46" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG44" t="n">
+      <c r="AG46" t="n">
         <v>5600</v>
       </c>
-      <c r="AH44" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>46</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>인터뷰</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>854396</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:42</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>살인자와의 인터뷰 [개정판][컬러연재]</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>총 53화/완결</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>53</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=3181357</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>3181357</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)
-평점
-9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료
-특종보다는 흥미를 느끼는 취재거리만 찾는 도윤에게 구 남친이 연락해 귀가 솔깃한 제안을 한다.바로 자신의 심리치료 환자인 연쇄 살인범과의 인터뷰를 진행하는 것.자신의 은밀한 사생활(?!)을 유지하고 싶었던 도윤은 이 ..</t>
-        </is>
-      </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>30.1만</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>301000</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>49</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해!</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>854132</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:43</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점]</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R46" t="n">
-        <v>6</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>14626941</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
-평점
-8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
-MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
-        </is>
-      </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
       <c r="AJ46" t="b">
         <v>0</v>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7672,26 +7672,26 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>화스트 페이스</t>
+          <t>나의 비발디</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>847905</t>
+          <t>854344</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:43</t>
+          <t>2026-09-21 12:50:24</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -7719,48 +7719,204 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>나의 비발디</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>나의 비발디 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>14580181</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>나의 비발디 (총 6화/미완결)
+평점
+10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료
+"갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
+        </is>
+      </c>
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>58</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>847905</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:50:24</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>화스트 페이스</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>24</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7768,162 +7924,6 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-09-14 13:34:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>55</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>나의 비발디</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>854344</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-09-14 12:51:43</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>나의 비발디</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>나의 비발디 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
-        <v>6</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>14580181</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>나의 비발디 (총 6화/미완결)
-평점
-10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료
-"갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
-        </is>
-      </c>
       <c r="Y48" t="b">
         <v>0</v>
       </c>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:25</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:25</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:02</t>
+          <t>2026-09-28 13:12:25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:02</t>
+          <t>2026-09-28 13:12:26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:03</t>
+          <t>2026-09-28 13:12:27</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:03</t>
+          <t>2026-09-28 13:12:27</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:03</t>
+          <t>2026-09-28 13:12:27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,42 +1384,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>누가 죄인인가</t>
+          <t>오! 나의 교주님</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>846782</t>
+          <t>841624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:04</t>
+          <t>2026-09-28 13:12:28</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue,fri</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue,fri</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1447,21 +1447,21 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>누가 죄인인가</t>
+          <t>오! 나의 교주님</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>누가 죄인인가 (총 37화/미완결)</t>
+          <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>총 37화/미완결</t>
+          <t>총 94화/미완결</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1470,181 +1470,25 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>평점 10.0 | 이승우 이승우 | 2026.09.06. | 총37화/미완결 | 30화 무료</t>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>평점 10.0 | 이승우 이승우 | 2026.09.06. | 총37화/미완결 | 30화 무료</t>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13634954</t>
+          <t>12998643</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
-        <is>
-          <t>누가 죄인인가 (총 37화/미완결)
-평점
-10.0 | 이승우 이승우 | 2026.09.06. | 총37화/미완결 | 30화 무료
-"나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
-        </is>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>841624</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:05</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님 (총 94화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>총 94화/미완결</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>94</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>12998643</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -1652,6 +1496,161 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>예쁨 컬렉션</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>844519</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:28</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>총 35화/미완결</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>35</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>13365963</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션 (총 35화/미완결)
+평점
+9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1695,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -1712,26 +1711,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>예쁨 컬렉션</t>
+          <t>포그랜드</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>844519</t>
+          <t>843116</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:05</t>
+          <t>2026-09-28 13:12:28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1759,21 +1758,21 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>19금 예쁨 컬렉션</t>
+          <t>포그랜드</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
+          <t>포그랜드 (총 44화/미완결)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>총 35화/미완결</t>
+          <t>총 44화/미완결</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1782,180 +1781,25 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>13365963</t>
+          <t>13177080</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
-        <is>
-          <t>19금 예쁨 컬렉션 (총 35화/미완결)
-평점
-9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
-        </is>
-      </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>포그랜드</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>843116</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:06</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>포그랜드</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>포그랜드 (총 44화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>총 44화/미완결</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>44</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>13177080</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)
 평점
@@ -1963,155 +1807,155 @@
 존재만으로도 미스터리한 국제 교도소 포그랜드.죄수 교화 목적으로 파견된 과학교사 단테 강은 한순간의 폭동 속에 포그랜드에 갇히게 된다.탈출하는 방법은 영도자가 되는 길 뿐.무너진 이성과 신성을 목도하라!단테의 아홉 ..</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>105</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C10" t="n">
         <v>20</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>분신</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845407&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>845407</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:06</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점]</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>총 176화/완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R10" t="n">
         <v>176</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=8833786</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>8833786</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)
 평점
@@ -2119,161 +1963,161 @@
 일해야 하고, 공부도 해야 하고, 밥도 먹어야 하고.‘왜 사람은 한 번에 한 가지 일밖에 못 하는 걸까.’상우는 항상 자신의 몸이 두 개였으면 좋겠다고 생각했다...그랬더니 몸이 두 개가 되었다.</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>105</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>1,022만</t>
         </is>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG10" t="n">
         <v>10220000</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847491&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>847491</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:06</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:28</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>총 28화/미완결</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R11" t="n">
         <v>28</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13704125</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>13704125</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)
 평점
@@ -2281,155 +2125,155 @@
 구남친에 대한 트라우마로 나쁜남자 취향을 가지게 된 수연은 현재의 남자친구에게 약간의 불만을 느끼지만 잘 지내고 있다.그러던 어느 날, 남자친구의 몸에 수연의 취향 그 자체인 '나쁜 남자'가 빙의하는데…이 저주. 풀어줘..</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>105</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C12" t="n">
+        <v>51</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>846110</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:07</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:29</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R12" t="n">
         <v>30</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>13567690</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)
 평점
@@ -2437,155 +2281,155 @@
 서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>105</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>53</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C13" t="n">
+        <v>54</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>851671</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:07</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:29</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R13" t="n">
         <v>5</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2593,155 +2437,155 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>105</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>82</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C14" t="n">
+        <v>84</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>812414</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:08</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:30</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R14" t="n">
         <v>128</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>9895056</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2749,155 +2593,155 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>105</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE14" t="n">
         <v>2</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>846109</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:09</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:31</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점]</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R15" t="n">
         <v>32</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>13566546</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)
 평점
@@ -2905,155 +2749,155 @@
 [진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>105</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C16" t="n">
         <v>10</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>834033</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:09</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:31</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R16" t="n">
         <v>87</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -3061,155 +2905,155 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>105</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C17" t="n">
         <v>31</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>846106</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:10</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:32</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 29화/미완결</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R17" t="n">
         <v>29</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>13575121</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3217,155 +3061,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>105</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C18" t="n">
+        <v>51</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단말인가</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853619&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>853619</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:10</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:32</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R18" t="n">
         <v>6</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14563924</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>14563924</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)
 평점
@@ -3373,155 +3217,155 @@
 타인의 시선속에서만 살아왔던 정숙녀(23세, 공시생)는 지쳤다. 좋아하는 것도 없고 해야 될 일들만 가득한 인생... 더는 이렇게 살기 싫어!! 기분전환이라도 할까 들어간 미용실에서. 어랏? 뿅! 대머리가 되어버렸다. 오늘부터 대머..</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>89</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C19" t="n">
+        <v>88</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>850210</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:12</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:34</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R19" t="n">
         <v>14</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3529,155 +3373,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C20" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>853278</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:13</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:34</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R20" t="n">
         <v>6</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>14532341</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)
 평점
@@ -3685,155 +3529,155 @@
 살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:13</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:34</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R21" t="n">
         <v>8</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3841,155 +3685,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:13</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:35</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R22" t="n">
         <v>80</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3997,155 +3841,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE22" t="n">
         <v>3</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>69</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C23" t="n">
+        <v>73</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:15</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:36</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R23" t="n">
         <v>10</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4153,6 +3997,162 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>89</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>장난질</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854375&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>854375</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:37</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>장난질 [독점]</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>장난질 [독점] (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>6</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>평점 9.0 | 진해, 봄그린 히아 | 2026.09.23. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>평점 9.0 | 진해, 봄그린 히아 | 2026.09.23. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14654634</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>14654634</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>장난질 [독점] (총 6화/미완결)
+평점
+9.0 | 진해, 봄그린 히아 | 2026.09.23. | 총6화/미완결 | 1화 무료
+[매주 목요일 연재][어머니를 위한 복수였다. 그것이 다였다. 진심으로 사랑에 빠지기 전까지는.]어머니와 함께 선암재에 먹고 살며 지냈던 소이.어느 날 어머니가 억울한 죽음을 당하며, 그에 따른 복수를 결심한다.지긋지긋한..</t>
+        </is>
+      </c>
       <c r="Y24" t="b">
         <v>0</v>
       </c>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>reused_existing_product_no</t>
+          <t>searched_series</t>
         </is>
       </c>
       <c r="AJ24" t="b">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:16</t>
+          <t>2026-09-28 13:12:38</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:16</t>
+          <t>2026-09-28 13:12:38</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:16</t>
+          <t>2026-09-28 13:12:38</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:16</t>
+          <t>2026-09-28 13:12:38</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:17</t>
+          <t>2026-09-28 13:12:39</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:18</t>
+          <t>2026-09-28 13:12:40</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:18</t>
+          <t>2026-09-28 13:12:40</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:18</t>
+          <t>2026-09-28 13:12:40</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:19</t>
+          <t>2026-09-28 13:12:42</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:19</t>
+          <t>2026-09-28 13:12:42</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:19</t>
+          <t>2026-09-28 13:12:42</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:20</t>
+          <t>2026-09-28 13:12:43</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:20</t>
+          <t>2026-09-28 13:12:43</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:21</t>
+          <t>2026-09-28 13:12:43</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:23</t>
+          <t>2026-09-28 13:12:46</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:23</t>
+          <t>2026-09-28 13:12:46</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -6729,22 +6729,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>어린 아내와 나쁜 짓</t>
+          <t>시루/24/1km</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>851385</t>
+          <t>850068</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:23</t>
+          <t>2026-09-28 13:12:46</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6772,48 +6772,203 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
+          <t>19금 시루/24/1km</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km (총 12화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>총 12화/미완결</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>12</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>14081030</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km (총 12화/미완결)
+평점
+10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="Y41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>851385</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:46</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>어린 아내와 나쁜 짓</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>8</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14245757</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>14245757</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)
 평점
@@ -6821,161 +6976,6 @@
 절망의 끝에서 나를 구원해준 남자, 범도건.작고 지켜야할 애기님이라며 내 고백을 짓밞았던 그때와는 다르게...이 남자, 남편 역할을 해도 너무 잘한다.낮에는 세상 든든한 보호자이던 그가 밤만 되면 맹수처럼 집착하며 나를 ..</t>
         </is>
       </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>11</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>시루/24/1km</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>850068</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:23</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>19금 시루/24/1km</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>19금 시루/24/1km (총 12화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>총 12화/미완결</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
-        <v>12</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>14081030</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>19금 시루/24/1km (총 12화/미완결)
-평점
-10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
-        </is>
-      </c>
       <c r="Y42" t="b">
         <v>0</v>
       </c>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:23</t>
+          <t>2026-09-28 13:12:47</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:24</t>
+          <t>2026-09-28 13:12:47</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -7354,26 +7354,26 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>꿈에서 본 그놈이 대단해!</t>
+          <t>나의 비발디</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>854132</t>
+          <t>854344</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:24</t>
+          <t>2026-09-28 13:12:47</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>꿈에서 본 그놈이 대단해! [독점]</t>
+          <t>나의 비발디</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
+          <t>나의 비발디 (총 6화/미완결)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7424,25 +7424,181 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>14580181</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>나의 비발디 (총 6화/미완결)
+평점
+10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료
+"갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
+        </is>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>49</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해!</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>854132</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:47</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점]</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>6</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>14626941</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
 평점
@@ -7450,155 +7606,155 @@
 MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>105</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>47</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="n">
+        <v>51</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>서바이브</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>838594</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:24</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:12:47</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="N47" t="n">
         <v>2</v>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>42</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7606,213 +7762,57 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>100</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE46" t="n">
+      <c r="AE47" t="n">
         <v>2</v>
       </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG46" t="n">
+      <c r="AG47" t="n">
         <v>5600</v>
       </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:34:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>49</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>나의 비발디</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>854344</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:24</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>나의 비발디</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>나의 비발디 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
-        <v>6</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>14580181</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>나의 비발디 (총 6화/미완결)
-평점
-10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료
-"갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
-        </is>
-      </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
       <c r="AJ47" t="b">
         <v>0</v>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:24</t>
+          <t>2026-09-28 13:12:48</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:25</t>
+          <t>2026-09-28 13:12:48</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:25</t>
+          <t>2026-09-28 13:12:49</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-09-21 13:34:37</t>
+          <t>2026-09-28 13:56:18</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:38</t>
+          <t>2026-10-19 12:41:46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:39</t>
+          <t>2026-10-19 12:41:46</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -926,26 +926,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>망플루언서</t>
+          <t>우리들의 속사정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850526&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855893&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>850526</t>
+          <t>855893</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:39</t>
+          <t>2026-10-19 12:41:47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -973,48 +973,204 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>우리들의 속사정</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>우리들의 속사정 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 강문송 아와와 | 2026.10.11. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 강문송 아와와 | 2026.10.11. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14834100</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>14834100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>우리들의 속사정 (총 6화/미완결)
+평점
+10.0 | 강문송 아와와 | 2026.10.11. | 총6화/미완결 | 1화 무료
+모든 게 잘 맞지만 딱 하나! 속궁합이 맞지 않는다면?완벽한 궁합을 위해 고군분투하는 사회 초년생들의 웃픈 속사정 로맨스!</t>
+        </is>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>망플루언서</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850526&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>850526</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:41:47</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>망플루언서</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>망플루언서 (총 12화/미완결)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>총 12화/미완결</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>12</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>평점 10.0 | 망순 망순 | 2026.06.14. | 총12화/미완결 | 6화 무료</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>평점 10.0 | 망순 망순 | 2026.06.14. | 총12화/미완결 | 6화 무료</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14140191</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>14140191</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>망플루언서 (총 12화/미완결)
 평점
@@ -1022,155 +1178,155 @@
 대중의 관심을 먹고 사는 빛나는 직업 '인플루언서!'보여지는 모습과 달리 그들의 숨겨진 추악한 비밀들을 폭로하는 유명 렉카 너튜브 채널 '셀럽 쓰레기통'그 채널을 운영하는 두 여자, 선미와 주원의 이야기."거짓으로 돈을 ..</t>
         </is>
       </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
         <v>105</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>57</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C6" t="n">
+        <v>59</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=826381&amp;tab=mon</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>826381</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:40</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:41:47</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법 (총 84화/미완결)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>총 84화/미완결</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>84</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>평점 9.9 | 류호, 황도톨 양담 | 2026.06.14. | 총84화/미완결 | 78화 무료</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>평점 9.9 | 류호, 황도톨 양담 | 2026.06.14. | 총84화/미완결 | 78화 무료</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11152272</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>11152272</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법 (총 84화/미완결)
 평점
@@ -1178,161 +1334,161 @@
 [살아생전 즐겨보던 소설에 환생했다.] 너무 진부하다구요? 아닐 걸요!왜냐면 그 소설이... 19금 피폐물이거든요...! ̗̀(ꀬ⏖ꀬ∴)예쁘고 상냥한 여주인공의 동생으로 환생했지만, 언니의 새드엔딩을 지켜볼 수 없었던 레나티..</t>
         </is>
       </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
         <v>105</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>216.7만</t>
         </is>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG6" t="n">
         <v>2167000</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>61</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>페일 블루 아이즈</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849898&amp;tab=mon</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>849898</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:40</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:41:47</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>페일 블루 아이즈</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>페일 블루 아이즈 (총 13화/미완결)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>총 13화/미완결</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>13</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>평점 9.9 | LICO, 피숙혜 당도삼십 | 2026.06.14. | 총13화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>평점 9.9 | LICO, 피숙혜 당도삼십 | 2026.06.14. | 총13화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14051143</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>14051143</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>페일 블루 아이즈 (총 13화/미완결)
 평점
@@ -1340,155 +1496,155 @@
 주은은 자신을 늘 외롭게 만드는 가족을 떠나 홀연히 영국으로 향한다. 그곳에서 만난 창백한 푸른눈의 남자, 에덴. 조악한 문신으로 온몸을 뒤덮은, 쓰레기 같은 펑크를 노래하는, 주변의 모든 여자를 열병에 들끓게 만드는, 하..</t>
         </is>
       </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
         <v>105</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>88</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="n">
+        <v>87</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>누가 죄인인가</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>846782</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:41</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:41:48</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>누가 죄인인가</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>누가 죄인인가 (총 41화/미완결)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>총 41화/미완결</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>41</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>평점 10.0 | 이승우 이승우 | 2026.10.04. | 총41화/미완결 | 34화 무료</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>평점 10.0 | 이승우 이승우 | 2026.10.04. | 총41화/미완결 | 34화 무료</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>13634954</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>누가 죄인인가 (총 41화/미완결)
 평점
@@ -1496,162 +1652,6 @@
 "나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
         </is>
       </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>월</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>121</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>우리들의 속사정</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855893&amp;tab=mon</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>855893</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:41</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>우리들의 속사정</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>우리들의 속사정 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>6</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 강문송 아와와 | 2026.10.11. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 강문송 아와와 | 2026.10.11. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14834100</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>14834100</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>우리들의 속사정 (총 6화/미완결)
-평점
-10.0 | 강문송 아와와 | 2026.10.11. | 총6화/미완결 | 1화 무료
-모든 게 잘 맞지만 딱 하나! 속궁합이 맞지 않는다면?완벽한 궁합을 위해 고군분투하는 사회 초년생들의 웃픈 속사정 로맨스!</t>
-        </is>
-      </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ8" t="b">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:41</t>
+          <t>2026-10-19 12:41:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:49</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:49</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:50</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:50</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:43</t>
+          <t>2026-10-19 12:41:51</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:44</t>
+          <t>2026-10-19 12:41:52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:44</t>
+          <t>2026-10-19 12:41:52</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:45</t>
+          <t>2026-10-19 12:41:52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:45</t>
+          <t>2026-10-19 12:41:54</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:46</t>
+          <t>2026-10-19 12:41:54</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:46</t>
+          <t>2026-10-19 12:41:55</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:47</t>
+          <t>2026-10-19 12:41:55</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:48</t>
+          <t>2026-10-19 12:41:56</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:48</t>
+          <t>2026-10-19 12:41:56</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -4368,26 +4368,26 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>당신에게 얽힌 채</t>
+          <t>순결을 그대에게</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821589&amp;tab=thu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>849879</t>
+          <t>821589</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:48</t>
+          <t>2026-10-19 12:41:56</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -4415,48 +4415,204 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>순결을 그대에게</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>순결을 그대에게 (총 29화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>총 29화/미완결</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 지공 지공 | 2024.07.31. | 총29화/미완결 | 전화 무료</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 지공 지공 | 2024.07.31. | 총29화/미완결 | 전화 무료</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=10749793</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>10749793</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>순결을 그대에게 (총 29화/미완결)
+평점
+10.0 | 지공 지공 | 2024.07.31. | 총29화/미완결 | 전화 무료
+원치 않는 결혼을 피하기 위해 소꿉친구인 딘에게 순결을 잃으려는 세라.하지만 딘의 모습이 어딘가 서툴다.“너 혹시 처음이야?”주인과 하인. 신분 차이를 넘나드는 첫사랑 로맨스.</t>
+        </is>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>75</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>849879</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:41:56</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>당신에게 얽힌 채</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>10</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4464,162 +4620,6 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>96</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>순결을 그대에게</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=821589&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>821589</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:49</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>순결을 그대에게</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>순결을 그대에게 (총 29화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>총 29화/미완결</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>29</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 지공 지공 | 2024.07.31. | 총29화/미완결 | 전화 무료</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 지공 지공 | 2024.07.31. | 총29화/미완결 | 전화 무료</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=10749793</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>10749793</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>순결을 그대에게 (총 29화/미완결)
-평점
-10.0 | 지공 지공 | 2024.07.31. | 총29화/미완결 | 전화 무료
-원치 않는 결혼을 피하기 위해 소꿉친구인 딘에게 순결을 잃으려는 세라.하지만 딘의 모습이 어딘가 서툴다.“너 혹시 처음이야?”주인과 하인. 신분 차이를 넘나드는 첫사랑 로맨스.</t>
-        </is>
-      </c>
       <c r="Y27" t="b">
         <v>0</v>
       </c>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ27" t="b">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:49</t>
+          <t>2026-10-19 12:41:57</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:49</t>
+          <t>2026-10-19 12:41:57</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:49</t>
+          <t>2026-10-19 12:41:57</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:49</t>
+          <t>2026-10-19 12:41:57</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:50</t>
+          <t>2026-10-19 12:41:58</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:50</t>
+          <t>2026-10-19 12:41:58</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:51</t>
+          <t>2026-10-19 12:41:59</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -5790,26 +5790,26 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>사탄의 순애</t>
+          <t>죽여주는 캐스팅</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>845378</t>
+          <t>843866</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:51</t>
+          <t>2026-10-19 12:41:59</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -5837,48 +5837,204 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>죽여주는 캐스팅 [독점]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>총 42화/미완결</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>42</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>13253015</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
+평점
+9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료
+영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
+        </is>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>79</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>사탄의 순애</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>845378</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:41:59</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>35</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5886,162 +6042,6 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>74</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>843866</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:51</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅 [독점]</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>총 42화/미완결</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>42</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>13253015</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
-평점
-9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료
-영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
-        </is>
-      </c>
       <c r="Y36" t="b">
         <v>0</v>
       </c>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:52</t>
+          <t>2026-10-19 12:42:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:52</t>
+          <t>2026-10-19 12:42:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:52</t>
+          <t>2026-10-19 12:42:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:53</t>
+          <t>2026-10-19 12:42:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:53</t>
+          <t>2026-10-19 12:42:01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6880,26 +6880,26 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>데스루프</t>
+          <t>메이드</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854905&amp;tab=sat</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>852086</t>
+          <t>854905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:54</t>
+          <t>2026-10-19 12:42:01</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -6927,48 +6927,210 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>마이 페어 메이드</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>마이 페어 메이드 (총 85화/완결)</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>총 85화/완결</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>85</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 솔체/DIAN 샌도 | 2023.09.29. | 총85화/완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 솔체/DIAN 샌도 | 2023.09.29. | 총85화/완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=8033729</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>8033729</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>마이 페어 메이드 (총 85화/완결)
+평점
+9.8 | 솔체/DIAN 샌도 | 2023.09.29. | 총85화/완결 | 3화 무료
+특기가 청소인 귀여운 메이드 샌디, 까칠한 바람둥이 도련님 킬리언의 약혼녀가 되다!어느 번개 치던 날 사교계 최고 미녀인 알렉산드라에게 빙의 된 샌디.평소 침 흘리며 바라보던 공작가 도련님 킬리언의 약혼녀가 되어 있다..</t>
+        </is>
+      </c>
+      <c r="Y42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>93만</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>930000</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>67</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>852086</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:42:01</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>데스루프</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>6</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>14366954</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6976,162 +7138,6 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
-      <c r="Y42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>80</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>메이드</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854905&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>854905</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:54</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>마이 페어 메이드</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>마이 페어 메이드 (총 85화/완결)</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>총 85화/완결</t>
-        </is>
-      </c>
-      <c r="R43" t="n">
-        <v>85</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 솔체/DIAN 샌도 | 2023.09.29. | 총85화/완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 솔체/DIAN 샌도 | 2023.09.29. | 총85화/완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=8033729</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>8033729</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>마이 페어 메이드 (총 85화/완결)
-평점
-9.8 | 솔체/DIAN 샌도 | 2023.09.29. | 총85화/완결 | 3화 무료
-특기가 청소인 귀여운 메이드 샌디, 까칠한 바람둥이 도련님 킬리언의 약혼녀가 되다!어느 번개 치던 날 사교계 최고 미녀인 알렉산드라에게 빙의 된 샌디.평소 침 흘리며 바라보던 공작가 도련님 킬리언의 약혼녀가 되어 있다..</t>
-        </is>
-      </c>
       <c r="Y43" t="b">
         <v>0</v>
       </c>
@@ -7148,33 +7154,27 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>matched</t>
+          <t>review_needed</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>first_non_compilation_numeric_download</t>
+          <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>93만</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>930000</v>
-      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>not_found</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ43" t="b">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:55</t>
+          <t>2026-10-19 12:42:03</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:56</t>
+          <t>2026-10-19 12:42:03</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:56</t>
+          <t>2026-10-19 12:42:03</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:56</t>
+          <t>2026-10-19 12:42:03</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -7821,26 +7821,26 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>나의 비발디</t>
+          <t>적귀</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855665&amp;tab=sun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>854344</t>
+          <t>855665</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:56</t>
+          <t>2026-10-19 12:42:03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -7864,16 +7864,16 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>나의 비발디</t>
+          <t>적귀</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>나의 비발디 (총 6화/미완결)</t>
+          <t>적귀 (총 6화/미완결)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -7891,25 +7891,181 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
+          <t>평점 10.0 | 혜성 이석재 | 2026.10.03. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 혜성 이석재 | 2026.10.03. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14812060</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>14812060</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>적귀 (총 6화/미완결)
+평점
+10.0 | 혜성 이석재 | 2026.10.03. | 총6화/미완결 | 1화 무료
+폭력과 욕망이 들끓던 1980년대. 임광천과 조도원, 두 남자가 뒷세계에 도전장을 내민다. 그들은 목표는 전국의 주먹을 꺾고 누구도 올라서지 못했던 정점. “전국제패” 〈부활남〉, 〈한림체육관〉의 최강자 임광천, 그의 전..</t>
+        </is>
+      </c>
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>47</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>나의 비발디</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>854344</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:42:04</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>나의 비발디</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>나의 비발디 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>14580181</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>나의 비발디 (총 6화/미완결)
 평점
@@ -7917,155 +8073,311 @@
 "갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
         <v>105</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr">
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>42</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>지옥심판</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>854096</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:42:04</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>지옥심판</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>총 7화/미완결</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>7</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>14622042</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)
+평점
+9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
+죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
+        </is>
+      </c>
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>51</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>인터뷰</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>854396</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:56</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:42:04</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>살인자와의 인터뷰 [개정판][컬러연재]</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>총 53화/완결</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R51" t="n">
         <v>53</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=3181357</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>3181357</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)
 평점
@@ -8073,324 +8385,6 @@
 특종보다는 흥미를 느끼는 취재거리만 찾는 도윤에게 구 남친이 연락해 귀가 솔깃한 제안을 한다.바로 자신의 심리치료 환자인 연쇄 살인범과의 인터뷰를 진행하는 것.자신의 은밀한 사생활(?!)을 유지하고 싶었던 도윤은 이 ..</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>30.1만</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>301000</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>44</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>적귀</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855665&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>855665</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:56</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>적귀</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>적귀 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R50" t="n">
-        <v>6</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 혜성 이석재 | 2026.10.03. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 혜성 이석재 | 2026.10.03. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14812060</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>14812060</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>적귀 (총 6화/미완결)
-평점
-10.0 | 혜성 이석재 | 2026.10.03. | 총6화/미완결 | 1화 무료
-폭력과 욕망이 들끓던 1980년대. 임광천과 조도원, 두 남자가 뒷세계에 도전장을 내민다. 그들은 목표는 전국의 주먹을 꺾고 누구도 올라서지 못했던 정점. “전국제패” 〈부활남〉, 〈한림체육관〉의 최강자 임광천, 그의 전..</t>
-        </is>
-      </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>2026-10-12 14:31:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>47</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>854096</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:56</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>총 7화/미완결</t>
-        </is>
-      </c>
-      <c r="R51" t="n">
-        <v>7</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>14622042</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)
-평점
-9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
-죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
-        </is>
-      </c>
       <c r="Y51" t="b">
         <v>0</v>
       </c>
@@ -8407,22 +8401,28 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>review_needed</t>
+          <t>matched</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>non_compilation_but_download_not_ok</t>
+          <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>30.1만</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>301000</v>
+      </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:57</t>
+          <t>2026-10-19 12:42:04</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:57</t>
+          <t>2026-10-19 12:42:04</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:58</t>
+          <t>2026-10-19 12:42:05</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:58</t>
+          <t>2026-10-19 12:42:05</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>2026-10-12 14:31:25</t>
+          <t>2026-10-19 13:25:54</t>
         </is>
       </c>
     </row>
